--- a/HealthRI Imaging metadata model v0.1.0.xlsx
+++ b/HealthRI Imaging metadata model v0.1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Projects/Imaging-Metadata-Petal/health-ri-metadata-imaging/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB6B15C-2376-8F4E-8680-401364DD45E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C942A603-AAC6-F248-9147-7AD2247B1132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34400" yWindow="-28200" windowWidth="34400" windowHeight="26380" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34400" yWindow="-28200" windowWidth="34400" windowHeight="26380" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <sheet name="PETScanProtocol" sheetId="31" r:id="rId13"/>
     <sheet name="PeriodOfTime" sheetId="32" r:id="rId14"/>
     <sheet name="QuantitativeValue" sheetId="33" r:id="rId15"/>
-    <sheet name="CatalogueRecord" sheetId="10" state="hidden" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">CTImagingSessionProtocol!$A$1:$I$2</definedName>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="264">
   <si>
     <t>Property label</t>
   </si>
@@ -90,12 +89,6 @@
     <t>Cardinality</t>
   </si>
   <si>
-    <t>History (same as v1, changed from v1, new)</t>
-  </si>
-  <si>
-    <t>Source of constraint (HealthDCAT-AP, DCAT-AP NL)</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -117,9 +110,6 @@
     <t>1..n</t>
   </si>
   <si>
-    <t>DCAT-AP NL</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
@@ -171,126 +161,6 @@
     <t>dcat:startDate</t>
   </si>
   <si>
-    <t>Value / Controlled Vocabulary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">application profile </t>
-  </si>
-  <si>
-    <t>An Application Profile that the Dataset's metadata conforms to.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:conformsTo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:Standard </t>
-  </si>
-  <si>
-    <t xml:space="preserve">change type </t>
-  </si>
-  <si>
-    <t>The status of the catalogue record in the context of editorial flow of the dataset and data service descriptions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adms:status </t>
-  </si>
-  <si>
-    <t xml:space="preserve">skos:Concept </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0..1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">description </t>
-  </si>
-  <si>
-    <t>A free-text account of the record. This property can be repeated for parallel language versions of the description.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:description </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rdfs:Literal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0..n </t>
-  </si>
-  <si>
-    <t xml:space="preserve">language </t>
-  </si>
-  <si>
-    <t>A language used in the textual metadata describing titles, descriptions, etc. of the Dataset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:language </t>
-  </si>
-  <si>
-    <t>This property can be repeated if the metadata is provided in multiple languages.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:LinguisticSystem </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1..n </t>
-  </si>
-  <si>
-    <t xml:space="preserve">listing date </t>
-  </si>
-  <si>
-    <t>The date on which the description of the Dataset was included in the Catalogue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:issued </t>
-  </si>
-  <si>
-    <t xml:space="preserve">modification date </t>
-  </si>
-  <si>
-    <t>The most recent date on which the Catalogue entry was changed or modified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:modified </t>
-  </si>
-  <si>
-    <t xml:space="preserve">primary topic </t>
-  </si>
-  <si>
-    <t>A link to the Dataset, Data service or Catalog described in the record.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foaf:primaryTopic </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A catalogue record will refer to one entity in a catalogue. This can be either a Dataset or a Data Service. To ensure an unambigous reading of the cardinality the range is set to Catalogued Resource. However it is not the intend with this range to require the explicit use of the class Catalogued Record. As abstract class, an subclass should be used. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:Resource </t>
-  </si>
-  <si>
-    <t xml:space="preserve">source metadata </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The original metadata that was used in creating metadata for the Dataset. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:source </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dcat:CatalogRecord </t>
-  </si>
-  <si>
-    <t xml:space="preserve">title </t>
-  </si>
-  <si>
-    <t>A name given to the Catalogue Record.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dct:title </t>
-  </si>
-  <si>
-    <t>This property can be repeated for parallel language versions of the name.</t>
-  </si>
-  <si>
     <t>prefix</t>
   </si>
   <si>
@@ -982,13 +852,16 @@
   </si>
   <si>
     <t>The minimum and maximum of the radiopharmaceutical dose administered to the patient measured in MegaBecquerels (MBq) at the Radiopharmaceutical Start DateTime (0018,1078). See DICOM tag (0018,1074) Radionuclide Total Dose.</t>
+  </si>
+  <si>
+    <t>schema:Number</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1003,30 +876,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF473821"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0A53A8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1047,21 +896,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
@@ -1132,7 +968,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1148,12 +984,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1190,215 +1020,122 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1406,13 +1143,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1421,7 +1158,57 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="145">
+  <dxfs count="107">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -1468,6 +1255,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -1554,6 +1351,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1574,6 +1401,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1584,6 +1431,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -1648,7 +1555,47 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="2"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1698,6 +1645,46 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -1738,6 +1725,66 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -1778,6 +1825,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -1804,6 +1861,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -1844,6 +1921,46 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1868,6 +1985,46 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="2"/>
         </patternFill>
       </fill>
@@ -1904,6 +2061,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -1944,6 +2121,46 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -1968,46 +2185,6 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -2039,826 +2216,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4525,338 +3882,338 @@
   <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="41"/>
+      <c r="E2" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H3" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="64" x14ac:dyDescent="0.2">
+      <c r="A7" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>243</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="R1" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="D2" s="72"/>
-      <c r="E2" s="58" t="s">
-        <v>234</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="72" t="s">
-        <v>226</v>
-      </c>
-      <c r="H2" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-    </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>243</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>282</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="H3" s="69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="69" t="s">
-        <v>283</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="B8" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H8" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
-        <v>244</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>284</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="69" t="s">
+    </row>
+    <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="B6" s="69" t="s">
-        <v>285</v>
-      </c>
-      <c r="F6" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="64" x14ac:dyDescent="0.2">
-      <c r="A7" s="69" t="s">
+      <c r="F9" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="69" t="s">
-        <v>286</v>
-      </c>
-      <c r="F7" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H7" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="73" t="s">
-        <v>252</v>
-      </c>
-      <c r="B8" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="F8" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="69" t="s">
+      <c r="F10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="64" x14ac:dyDescent="0.2">
+      <c r="A11" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="B9" s="69" t="s">
-        <v>288</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H9" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="69" t="s">
+      <c r="F11" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="64" x14ac:dyDescent="0.2">
+      <c r="A12" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="B10" s="69" t="s">
-        <v>289</v>
-      </c>
-      <c r="F10" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H10" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="64" x14ac:dyDescent="0.2">
-      <c r="A11" s="73" t="s">
-        <v>251</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>290</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H11" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="64" x14ac:dyDescent="0.2">
-      <c r="A12" s="69" t="s">
+      <c r="F12" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="64" x14ac:dyDescent="0.2">
+      <c r="A13" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="B12" s="63" t="s">
-        <v>291</v>
-      </c>
-      <c r="F12" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H12" s="69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="64" x14ac:dyDescent="0.2">
-      <c r="A13" s="69" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="63" t="s">
-        <v>292</v>
-      </c>
-      <c r="F13" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H13" s="69" t="s">
-        <v>22</v>
+      <c r="F13" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2:F13">
-    <cfRule type="cellIs" dxfId="94" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="8" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1 F1:F13">
-    <cfRule type="cellIs" dxfId="91" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="87" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="51" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="50" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="85" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="49" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4892,200 +4249,200 @@
   <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.5" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.5" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="B2" s="64" t="s">
-        <v>296</v>
-      </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58" t="s">
-        <v>295</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57">
+      <c r="C2" s="26"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27">
         <v>1</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="B3" s="64" t="s">
-        <v>297</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
+      <c r="F3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="B4" s="69" t="s">
-        <v>298</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>22</v>
+      <c r="F4" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="B5" s="69" t="s">
-        <v>299</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>22</v>
+      <c r="F5" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="cellIs" dxfId="84" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F5">
+    <cfRule type="cellIs" dxfId="47" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="83" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F5">
-    <cfRule type="cellIs" dxfId="81" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="77" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="40" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="75" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="39" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5121,186 +4478,186 @@
   <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="68" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="68" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="68" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="55" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="25" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="B2" s="64" t="s">
-        <v>300</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="58" t="s">
-        <v>303</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="57">
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="31"/>
+      <c r="H2" s="27">
         <v>1</v>
       </c>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="44" t="s">
         <v>258</v>
       </c>
-      <c r="B3" s="75" t="s">
-        <v>301</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>22</v>
+      <c r="F3" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="44" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="75" t="s">
-        <v>302</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>22</v>
+      <c r="F4" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2:F4">
-    <cfRule type="cellIs" dxfId="74" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F4">
+    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="73" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F4">
-    <cfRule type="cellIs" dxfId="71" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="67" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="30" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="29" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5336,169 +4693,169 @@
   <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>304</v>
-      </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19" ht="96" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>261</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>305</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>22</v>
+      <c r="A3" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="64" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F3">
+    <cfRule type="cellIs" dxfId="27" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="63" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F3">
-    <cfRule type="cellIs" dxfId="61" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="57" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="20" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5534,228 +4891,214 @@
   <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:20" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
+      <c r="I1" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="16"/>
+      <c r="F2" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="68" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="68" t="s">
-        <v>166</v>
-      </c>
-      <c r="R1" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="68" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="33" t="s">
+      <c r="J2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C3" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="23" t="s">
+      <c r="D3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="G3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="H3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
       <c r="M3" s="1" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>157</v>
+        <v>107</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="H1 F1">
-    <cfRule type="cellIs" dxfId="51" priority="20" operator="equal">
+  <conditionalFormatting sqref="F1:F3">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+  <conditionalFormatting sqref="H1:H3">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5788,174 +5131,174 @@
   <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="B2" s="69" t="s">
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="C2" s="69" t="s">
-        <v>262</v>
-      </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="H2" s="57">
+      <c r="H2" s="27">
         <v>1</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>265</v>
-      </c>
-      <c r="C3" s="69" t="s">
-        <v>264</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="H3" s="15">
+      <c r="A3" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="44" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F3">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="43" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F3">
-    <cfRule type="cellIs" dxfId="41" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="37" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5982,710 +5325,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D9DD92-C939-4751-8A55-ABA6494CBB01}">
-  <dimension ref="A1:J38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="24.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5" style="6" customWidth="1"/>
-    <col min="3" max="3" width="53.5" style="6" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="54.5" style="6" customWidth="1"/>
-    <col min="6" max="6" width="22.1640625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.1640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="24">
-        <v>1</v>
-      </c>
-      <c r="I7" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="80" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="39">
-        <v>1</v>
-      </c>
-      <c r="I8" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="43" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="38"/>
-      <c r="G10" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="J10" s="40" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="13"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="9"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="9"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="9"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="9"/>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="9"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="9"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="3"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J10">
-    <sortCondition ref="A2:A10"/>
-  </sortState>
-  <conditionalFormatting sqref="A27:B28">
-    <cfRule type="cellIs" dxfId="34" priority="41" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="42" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="43" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="44" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D26:E28">
-    <cfRule type="cellIs" dxfId="30" priority="45" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="46" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="47" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="48" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="cellIs" dxfId="26" priority="51" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="52" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="53" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="54" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7 E8">
-    <cfRule type="cellIs" dxfId="22" priority="40" operator="equal">
-      <formula>"Not added"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F38">
-    <cfRule type="cellIs" dxfId="21" priority="33" operator="equal">
-      <formula>"Not added"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="36" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="37" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="38" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="39" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H11">
-    <cfRule type="cellIs" dxfId="16" priority="9" operator="greaterThan">
-      <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="10" operator="equal">
-      <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:H27 H36:H38">
-    <cfRule type="cellIs" dxfId="14" priority="49" operator="greaterThan">
-      <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="50" operator="equal">
-      <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1:I1 F1:F7">
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="17" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
-      <formula>"Conditional"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{9FFB3FDE-E91E-4928-B624-871FBDE5B4FE}">
-      <formula1>"Mandatory, Recommended, Optional, Conditional"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36:H38 H13:H27 H2:H11" xr:uid="{F575A745-2778-4980-A666-2F8CC8BA98C8}">
-      <formula1>"0..n, 0..1, 1, 1..n"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576" xr:uid="{B236D01E-79E6-4286-BC17-814A8BFC03E9}">
-      <formula1>"Identical to v1, Adapted from v1, new"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{C635322F-BE65-4D2A-9650-07C570FF1FCD}">
-      <formula1>"DCAT-AP v3, HealthDCAT-AP, DCAT-AP NL, HRI v1"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F7 F9:F38 E8" xr:uid="{DBDB35B3-BE51-4BAA-8353-197930219622}">
-      <formula1>"Mandatory, Recommended, Optional, Conditional, Not added"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1" xr:uid="{3F9E1045-B372-49CA-8B06-08188CFB15F9}"/>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E2C641-7C5D-47E8-9C29-F3A4B74AE3E2}">
   <dimension ref="A1"/>
@@ -6703,330 +5342,330 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>78</v>
+        <v>34</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="66" t="s">
-        <v>80</v>
+        <v>36</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" s="66" t="s">
-        <v>82</v>
+        <v>38</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="66" t="s">
-        <v>84</v>
+        <v>40</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>86</v>
+        <v>42</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="66" t="s">
-        <v>88</v>
+        <v>44</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="66" t="s">
-        <v>90</v>
+        <v>46</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="66" t="s">
-        <v>92</v>
+        <v>48</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" s="66" t="s">
-        <v>94</v>
+        <v>50</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="66" t="s">
-        <v>96</v>
+        <v>52</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="66" t="s">
-        <v>98</v>
+        <v>54</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="66" t="s">
-        <v>100</v>
+        <v>56</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="66" t="s">
-        <v>102</v>
+        <v>58</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="66" t="s">
-        <v>104</v>
+        <v>60</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" s="66" t="s">
-        <v>106</v>
+        <v>62</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="66" t="s">
-        <v>84</v>
+        <v>40</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="66" t="s">
-        <v>108</v>
+        <v>64</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="66" t="s">
-        <v>110</v>
+        <v>66</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="66" t="s">
-        <v>112</v>
+        <v>68</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="66" t="s">
-        <v>114</v>
+        <v>70</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>115</v>
-      </c>
-      <c r="B22" s="66" t="s">
-        <v>116</v>
+        <v>72</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="66" t="s">
-        <v>118</v>
+        <v>74</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B24" s="66" t="s">
-        <v>120</v>
+        <v>76</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="66" t="s">
-        <v>122</v>
+        <v>78</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B26" s="66" t="s">
-        <v>159</v>
+        <v>80</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>124</v>
-      </c>
-      <c r="B27" s="66" t="s">
-        <v>125</v>
+        <v>81</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="66" t="s">
-        <v>127</v>
+        <v>83</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="66" t="s">
-        <v>129</v>
+        <v>85</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>130</v>
-      </c>
-      <c r="B30" s="66" t="s">
-        <v>131</v>
+        <v>87</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>132</v>
-      </c>
-      <c r="B31" s="66" t="s">
-        <v>133</v>
+        <v>89</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" s="66" t="s">
-        <v>135</v>
+        <v>91</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>136</v>
-      </c>
-      <c r="B33" s="66" t="s">
-        <v>137</v>
+        <v>93</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="B39" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>206</v>
-      </c>
-      <c r="B40" s="66" t="s">
-        <v>207</v>
+        <v>163</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>222</v>
-      </c>
-      <c r="B41" s="66" t="s">
-        <v>223</v>
+        <v>179</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7077,7 +5716,7 @@
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" style="67" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" style="37" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.5" customWidth="1"/>
     <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
@@ -7087,233 +5726,233 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>18</v>
+        <v>117</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F1" s="67" t="s">
-        <v>171</v>
+        <v>127</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>128</v>
       </c>
       <c r="G1" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="H1" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" s="67" t="s">
-        <v>177</v>
+        <v>133</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>134</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="H2" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="66" t="s">
-        <v>182</v>
+        <v>136</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="H3" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C4" s="67" t="s">
-        <v>187</v>
-      </c>
-      <c r="D4" s="66" t="s">
-        <v>182</v>
+        <v>143</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="H4" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s">
-        <v>205</v>
-      </c>
-      <c r="C5" s="67" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="66" t="s">
-        <v>182</v>
+        <v>162</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="H5" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
-      </c>
-      <c r="C6" s="67" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="66" t="s">
-        <v>182</v>
+        <v>147</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="67" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="66" t="s">
-        <v>182</v>
+        <v>150</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="67" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="66" t="s">
-        <v>182</v>
+        <v>159</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="H8" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="66" t="s">
-        <v>182</v>
+        <v>159</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="H9" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="67" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="66" t="s">
-        <v>182</v>
+        <v>159</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="H10" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="H11" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="H12" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -7340,185 +5979,185 @@
   <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
+      <c r="I1" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="41"/>
+      <c r="E4" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="R1" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="58" t="s">
-        <v>232</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-    </row>
-    <row r="3" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>211</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>215</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="58" t="s">
-        <v>233</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="72" t="s">
-        <v>225</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="64" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="69" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="58" t="s">
-        <v>234</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="72" t="s">
-        <v>226</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
-        <v>213</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>217</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>15</v>
+      <c r="C5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -7527,40 +6166,40 @@
     <sortCondition ref="A2"/>
   </sortState>
   <conditionalFormatting sqref="F2:F5">
-    <cfRule type="cellIs" dxfId="144" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F5">
+    <cfRule type="cellIs" dxfId="105" priority="19" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="104" priority="20" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="21" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="143" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="17" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="18" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F5">
-    <cfRule type="cellIs" dxfId="141" priority="19" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="20" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="21" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="137" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="99" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="136" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="98" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="135" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="97" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7601,305 +6240,305 @@
   <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="70" t="s">
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="S1" s="70" t="s">
+      <c r="B2" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" s="27">
+        <v>1</v>
+      </c>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="39" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>218</v>
-      </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="58" t="s">
+      <c r="B6" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="42" t="s">
         <v>232</v>
       </c>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="H2" s="57">
-        <v>1</v>
-      </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-    </row>
-    <row r="3" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>227</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>268</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="C4" s="69" t="s">
+      <c r="B7" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="63" t="s">
-        <v>270</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="69" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="69" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="D6" s="72"/>
-      <c r="E6" s="58" t="s">
+    </row>
+    <row r="8" spans="1:19" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F6" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="72" t="s">
-        <v>225</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="73" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="69" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="69" t="s">
-        <v>272</v>
-      </c>
-      <c r="F8" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9" s="69" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="69" t="s">
-        <v>273</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="F9" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>15</v>
+      <c r="F9" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="B10" s="64" t="s">
-        <v>274</v>
-      </c>
-      <c r="E10" s="69" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>15</v>
+      <c r="E10" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2:F10">
-    <cfRule type="cellIs" dxfId="134" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F10">
+    <cfRule type="cellIs" dxfId="95" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="94" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="93" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="92" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="133" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F10">
-    <cfRule type="cellIs" dxfId="131" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="130" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="127" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="89" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="126" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="88" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="125" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="87" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7939,152 +6578,152 @@
   <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2">
-    <cfRule type="cellIs" dxfId="124" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F2">
+    <cfRule type="cellIs" dxfId="85" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="83" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="82" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="123" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F2">
-    <cfRule type="cellIs" dxfId="121" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="117" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="79" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="116" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="78" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="115" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="77" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8120,169 +6759,169 @@
   <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="68" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="68" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="68" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="68" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="68" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="68" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="55" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="25" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="69" t="s">
-        <v>238</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="57" t="s">
-        <v>280</v>
-      </c>
-      <c r="H2" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="H2" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:19" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="69" t="s">
-        <v>240</v>
-      </c>
-      <c r="E3" s="69" t="s">
-        <v>279</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>15</v>
+      <c r="A3" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="114" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F3">
+    <cfRule type="cellIs" dxfId="75" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="113" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="71" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F3">
-    <cfRule type="cellIs" dxfId="111" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="107" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="69" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="106" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="68" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="105" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="67" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8318,152 +6957,152 @@
   <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.5" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="68.83203125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="24.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" style="15" customWidth="1"/>
-    <col min="12" max="12" width="21.33203125" style="15" customWidth="1"/>
-    <col min="13" max="14" width="22" style="15" customWidth="1"/>
-    <col min="15" max="15" width="18.1640625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="16" style="15" customWidth="1"/>
-    <col min="17" max="19" width="25" style="15" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="15"/>
+    <col min="1" max="1" width="25.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="68.83203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="16" style="3" customWidth="1"/>
+    <col min="17" max="19" width="25" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="9.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:19" s="35" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="J1" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="70" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="70" t="s">
-        <v>162</v>
-      </c>
-      <c r="M1" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="N1" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="O1" s="70" t="s">
-        <v>164</v>
-      </c>
-      <c r="P1" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q1" s="70" t="s">
+      <c r="I1" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="R1" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="S1" s="70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" s="54" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="73" t="s">
-        <v>242</v>
-      </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="57" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57">
+      <c r="J1" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="O1" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="24" customFormat="1" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27">
         <v>1</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="F2">
-    <cfRule type="cellIs" dxfId="104" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="8" operator="equal">
       <formula>"Not added"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1 F1:F2">
+    <cfRule type="cellIs" dxfId="65" priority="11" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="12" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="63" priority="13" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="14" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="103" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="9" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="10" operator="equal">
       <formula>"needs review"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H1 F1:F2">
-    <cfRule type="cellIs" dxfId="101" priority="11" operator="equal">
-      <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="12" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="13" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="14" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="97" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="59" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="58" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",I2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="95" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="57" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8491,18 +7130,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Status xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">Draft</Status>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000B1A1CF98C819F4881BB4349588D0C85" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ff8ef391852eaca4511043a54bffd4a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cfc87205-1831-4b6c-a7b4-76d40079a43e" xmlns:ns3="221af607-abea-4d5e-830c-567dcc03c0ec" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="201dd8b781da46d5daa37e3355db44fe" ns2:_="" ns3:_="">
     <xsd:import namespace="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
@@ -8745,6 +7372,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Status xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">Draft</Status>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cfc87205-1831-4b6c-a7b4-76d40079a43e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="221af607-abea-4d5e-830c-567dcc03c0ec" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8755,17 +7394,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
-    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A23828-4FF7-4569-837D-B1B2C775409F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8784,6 +7412,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16D2CAB5-B21B-4A93-9D82-49FE3E36CF14}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cfc87205-1831-4b6c-a7b4-76d40079a43e"/>
+    <ds:schemaRef ds:uri="221af607-abea-4d5e-830c-567dcc03c0ec"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A00443-9B7C-473F-A198-CBEB23A0BCC5}">
   <ds:schemaRefs>

--- a/HealthRI Imaging metadata model v0.1.0.xlsx
+++ b/HealthRI Imaging metadata model v0.1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Projects/Imaging-Metadata-Petal/health-ri-metadata-imaging/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C942A603-AAC6-F248-9147-7AD2247B1132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DDB0E4-2784-6E48-98C8-D0D169E52E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34400" yWindow="-28200" windowWidth="34400" windowHeight="26380" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34400" yWindow="-28200" windowWidth="34400" windowHeight="26380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="14" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="265">
   <si>
     <t>Property label</t>
   </si>
@@ -855,6 +855,9 @@
   </si>
   <si>
     <t>schema:Number</t>
+  </si>
+  <si>
+    <t>Object to display the minimum and maximum value of a property.</t>
   </si>
 </sst>
 </file>
@@ -5941,12 +5944,15 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>155</v>
       </c>
       <c r="B12" t="s">
         <v>157</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>264</v>
       </c>
       <c r="D12" t="s">
         <v>156</v>

--- a/HealthRI Imaging metadata model v0.1.0.xlsx
+++ b/HealthRI Imaging metadata model v0.1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Projects/Imaging-Metadata-Petal/health-ri-metadata-imaging/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DDB0E4-2784-6E48-98C8-D0D169E52E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B62D47A-D5EF-B94D-881C-060162AC2FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34400" yWindow="-28200" windowWidth="34400" windowHeight="26380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,9 +488,6 @@
     <t>SIO.SIO_000999</t>
   </si>
   <si>
-    <t>An ImagingSessionProtocol describes a protocol used for creating the imaging sessions in this dataset. An imaging session is defined as an event which clinically would result in one report. An imaging session consists of one or more scans.</t>
-  </si>
-  <si>
     <t>CTImagingSessionProtocol</t>
   </si>
   <si>
@@ -518,9 +515,6 @@
     <t>hri:ScanProtocol</t>
   </si>
   <si>
-    <t>ScanProtocol describes the protocol used for one or multiple acquisitions (slices) using the same parameters on a patient, as part of an imaging session.</t>
-  </si>
-  <si>
     <t>An ScanProtocol for CT imaging.</t>
   </si>
   <si>
@@ -858,6 +852,12 @@
   </si>
   <si>
     <t>Object to display the minimum and maximum value of a property.</t>
+  </si>
+  <si>
+    <t>An ImagingSessionProtocol describes a protocol used for creating the imaging sessions in this dataset. An imaging session is defined as an event which clinically would result in one report. An imaging session consists of one or more scans. This corresponds to the level of a DICOM Study.</t>
+  </si>
+  <si>
+    <t>ScanProtocol describes the protocol used for one or multiple acquisitions (slices) using the same parameters on a patient, as part of an imaging session. This corresponds to the level of a DICOM Series.</t>
   </si>
 </sst>
 </file>
@@ -3930,7 +3930,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -3965,23 +3965,23 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D2" s="41"/>
       <c r="E2" s="28" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="41" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H2" s="39" t="s">
         <v>14</v>
@@ -4000,16 +4000,16 @@
     </row>
     <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H3" s="39">
         <v>1</v>
@@ -4020,7 +4020,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
@@ -4037,13 +4037,13 @@
     </row>
     <row r="5" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>12</v>
@@ -4054,16 +4054,16 @@
     </row>
     <row r="6" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="39" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H6" s="39" t="s">
         <v>19</v>
@@ -4071,16 +4071,16 @@
     </row>
     <row r="7" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" s="39" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H7" s="39" t="s">
         <v>19</v>
@@ -4088,16 +4088,16 @@
     </row>
     <row r="8" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="42" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F8" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H8" s="42" t="s">
         <v>19</v>
@@ -4105,16 +4105,16 @@
     </row>
     <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="39" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H9" s="39" t="s">
         <v>19</v>
@@ -4122,16 +4122,16 @@
     </row>
     <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="39" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H10" s="39" t="s">
         <v>19</v>
@@ -4139,16 +4139,16 @@
     </row>
     <row r="11" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H11" s="39" t="s">
         <v>19</v>
@@ -4156,16 +4156,16 @@
     </row>
     <row r="12" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F12" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H12" s="39" t="s">
         <v>19</v>
@@ -4173,16 +4173,16 @@
     </row>
     <row r="13" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H13" s="39" t="s">
         <v>19</v>
@@ -4297,7 +4297,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -4332,15 +4332,15 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>9</v>
@@ -4363,10 +4363,10 @@
     </row>
     <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>9</v>
@@ -4377,16 +4377,16 @@
     </row>
     <row r="4" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>19</v>
@@ -4394,16 +4394,16 @@
     </row>
     <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>19</v>
@@ -4526,7 +4526,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -4561,15 +4561,15 @@
     </row>
     <row r="2" spans="1:19" s="25" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="30"/>
       <c r="E2" s="28" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>9</v>
@@ -4592,16 +4592,16 @@
     </row>
     <row r="3" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -4609,16 +4609,16 @@
     </row>
     <row r="4" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>19</v>
@@ -4741,7 +4741,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -4776,10 +4776,10 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="28"/>
@@ -4788,7 +4788,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>19</v>
@@ -4807,16 +4807,16 @@
     </row>
     <row r="3" spans="1:19" ht="96" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -4939,7 +4939,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -5214,13 +5214,13 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
@@ -5228,7 +5228,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H2" s="27">
         <v>1</v>
@@ -5247,19 +5247,19 @@
     </row>
     <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H3" s="3">
         <v>1</v>
@@ -5657,18 +5657,18 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5773,7 +5773,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>135</v>
       </c>
@@ -5781,7 +5781,7 @@
         <v>136</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="D3" s="36" t="s">
         <v>139</v>
@@ -5792,13 +5792,13 @@
     </row>
     <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" t="s">
         <v>142</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="37" t="s">
         <v>143</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>144</v>
       </c>
       <c r="D4" s="36" t="s">
         <v>139</v>
@@ -5812,13 +5812,13 @@
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="36" t="s">
         <v>139</v>
@@ -5832,13 +5832,13 @@
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="37" t="s">
         <v>147</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>148</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>139</v>
@@ -5850,15 +5850,15 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" t="s">
         <v>149</v>
       </c>
-      <c r="B7" t="s">
-        <v>150</v>
-      </c>
       <c r="C7" s="37" t="s">
-        <v>151</v>
+        <v>264</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>139</v>
@@ -5869,19 +5869,19 @@
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" s="36" t="s">
         <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H8" t="s">
         <v>140</v>
@@ -5889,19 +5889,19 @@
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D9" s="36" t="s">
         <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H9" t="s">
         <v>140</v>
@@ -5909,19 +5909,19 @@
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D10" s="36" t="s">
         <v>139</v>
       </c>
       <c r="E10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H10" t="s">
         <v>140</v>
@@ -5946,19 +5946,19 @@
     </row>
     <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" t="s">
         <v>155</v>
       </c>
-      <c r="B12" t="s">
-        <v>157</v>
-      </c>
       <c r="C12" s="37" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -5973,6 +5973,7 @@
     <hyperlink ref="D10" r:id="rId8" display="http://semanticscience.org/resource/SIO_000999" xr:uid="{F4839171-3961-FD48-9C84-220699602213}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -6030,7 +6031,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -6065,23 +6066,23 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D2" s="40"/>
       <c r="E2" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>14</v>
@@ -6100,23 +6101,23 @@
     </row>
     <row r="3" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D3" s="41"/>
       <c r="E3" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="41" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
@@ -6124,23 +6125,23 @@
     </row>
     <row r="4" spans="1:19" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" s="39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D4" s="41"/>
       <c r="E4" s="28" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="41" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
@@ -6148,13 +6149,13 @@
     </row>
     <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>12</v>
@@ -6291,7 +6292,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -6326,23 +6327,23 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D2" s="40"/>
       <c r="E2" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="40" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H2" s="27">
         <v>1</v>
@@ -6361,10 +6362,10 @@
     </row>
     <row r="3" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>9</v>
@@ -6381,7 +6382,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>16</v>
@@ -6398,16 +6399,16 @@
     </row>
     <row r="5" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
@@ -6415,23 +6416,23 @@
     </row>
     <row r="6" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D6" s="41"/>
       <c r="E6" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>13</v>
@@ -6439,10 +6440,10 @@
     </row>
     <row r="7" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>24</v>
@@ -6459,10 +6460,10 @@
     </row>
     <row r="8" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F8" s="27" t="s">
         <v>12</v>
@@ -6476,13 +6477,13 @@
     </row>
     <row r="9" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>12</v>
@@ -6493,13 +6494,13 @@
     </row>
     <row r="10" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="39" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>12</v>
@@ -6629,7 +6630,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -6664,15 +6665,15 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="28"/>
       <c r="E2" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>9</v>
@@ -6810,7 +6811,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -6845,10 +6846,10 @@
     </row>
     <row r="2" spans="1:19" s="25" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="30"/>
@@ -6857,7 +6858,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H2" s="27" t="s">
         <v>14</v>
@@ -6876,13 +6877,13 @@
     </row>
     <row r="3" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E3" s="39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>12</v>
@@ -7008,7 +7009,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J1" s="23" t="s">
         <v>8</v>
@@ -7043,15 +7044,15 @@
     </row>
     <row r="2" spans="1:19" s="24" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>9</v>
